--- a/public/StructureDefinition-pghd-electrocardiogram.xlsx
+++ b/public/StructureDefinition-pghd-electrocardiogram.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T16:46:43-05:00</t>
+    <t>2026-04-23T16:43:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-electrocardiogram.xlsx
+++ b/public/StructureDefinition-pghd-electrocardiogram.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T16:43:45-05:00</t>
+    <t>2026-04-23T17:08:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-electrocardiogram.xlsx
+++ b/public/StructureDefinition-pghd-electrocardiogram.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T17:08:04-05:00</t>
+    <t>2026-06-11T13:06:45-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-electrocardiogram.xlsx
+++ b/public/StructureDefinition-pghd-electrocardiogram.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T13:06:45-06:00</t>
+    <t>2026-06-11T16:28:41-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
